--- a/data/output_qaqc/qaqc_menage.xlsx
+++ b/data/output_qaqc/qaqc_menage.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Résumé général" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sexe CM" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Niveau études CM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Situation matrimoniale" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Scolarisation CM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Régions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Milieu" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Qualité des données" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Notes méthodologiques" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Résumé général" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sexe CM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Niveau études CM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation matrimoniale" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scolarisation CM" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statut emploi CM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secteur activité CM" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Régions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milieu" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qualité des données" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes méthodologiques" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -598,7 +600,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -626,313 +628,817 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Ménages ordinaires</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>188,550  (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ménages collectifs</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>0  (0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TAILLE DU MÉNAGE</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Taille moyenne</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>8.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Taille médiane</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Écart-type</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Maximum</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>1–2 membres</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>24,346  (12.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>3–5 membres</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>40,869  (21.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>6–10 membres</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>66,470  (35.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>11–20 membres</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>45,789  (24.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>21–50 membres</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>10,874  (5.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Plus de 50 membres</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>202  (0.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ÂGE DU CHEF DE MÉNAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Âge moyen</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>49.6 ans</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Âge médian</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>49 ans</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Écart-type</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>14.6 ans</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>10 ans</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Maximum</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>112 ans</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Moins de 25 ans</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>5,136  (2.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>25–34 ans</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>23,940  (12.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>35–44 ans</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>44,866  (23.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>45–54 ans</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>45,488  (24.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>55–64 ans</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>36,732  (19.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>65 ans et plus</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>32,388  (17.2%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>QUALITÉ DES DONNÉES - VALEURS MANQUANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Nb manquants</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Taux (%)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>niveau_etudes_cm</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>35077</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Modéré 5–20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>men_id</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>departement</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>milieu_residence</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>commune</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>taille_menage</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>sexe_cm</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Taille moyenne</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>8.87</t>
+          <t>age_cm</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Taille médiane</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>type_menage</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Écart-type</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>6.75</t>
+          <t>scolarisation_cm</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>situation_matrimoniale_cm</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Maximum</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>125</t>
+          <t>statut_emploi_cm</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>1–2 membres</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>24,346  (12.9%)</t>
+          <t>branche_isic_cm</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3–5 membres</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>40,869  (21.7%)</t>
+          <t>secteur_instit_cm</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>6–10 membres</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>66,470  (35.3%)</t>
+          <t>nb_enfants_moins5ans</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>11–20 membres</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>45,789  (24.3%)</t>
+          <t>nb_femmes_15_49</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>21–50 membres</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>10,874  (5.8%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Plus de 50 membres</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>202  (0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>ÂGE DU CHEF DE MÉNAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Valeur</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Âge moyen</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>49.6 ans</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Âge médian</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>49 ans</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Écart-type</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>14.6 ans</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>10 ans</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Maximum</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>112 ans</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Moins de 25 ans</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>5,136  (2.7%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>25–34 ans</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>23,940  (12.7%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>35–44 ans</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>44,866  (23.8%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>45–54 ans</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>45,488  (24.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>55–64 ans</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>36,732  (19.5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>65 ans et plus</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>32,388  (17.2%)</t>
+          <t>ratio_dependance</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Complet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>NOTES MÉTHODOLOGIQUES - DÉCISIONS DE TRAITEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>TRAITEMENT DES VALEURS ABERRANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Explication</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Âge du CM (age_cm)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Bornes définies : [0, 120] ans. Toute valeur hors de ces bornes est remplacée par NaN. Justification : aucun être humain ne peut avoir un âge négatif ou supérieur à 120 ans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Taille du ménage (taille_menage)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Seuil fixé au 99e percentile observé = 125 membres. Valeurs &gt; 125 remplacées par NaN. Justification empirique : distribution observée - P50=12, P75=46, P90=78, P99=125.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>CONTRÔLES DE COHÉRENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Explication</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Sexe vs situation matrimoniale</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Un CM de sexe masculin ne peut pas être déclaré épouse en polygamie. Action : situation_matrimoniale_cm - NaN.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1741,6 +2247,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>STATUT D'EMPLOI DU CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Modalité</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Proportion (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Occupé</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>92363</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A la recherche d un premier emploi</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>25360</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>13.45</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Autres inactifs, à préciser</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>21533</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>11.42</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Personne du 3e age non pensionnée</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>14998</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Occupé au foyer</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>14927</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Personne du 3e age pensionnée (FNR ou IPRES)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>7796</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Chômeur ayant travaillé</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>4922</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Rentier</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4151</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Etudiant/elève</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>188,550</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>SECTEUR D'ACTIVITÉ DU CM (ISIC Rev 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Modalité</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Proportion (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>96187</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>51.01</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Informel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>44362</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>23.53</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>29908</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>15.86</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Privé formel</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>17850</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>9.470000000000001</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ISBLSM (ONG, ASC, Fondations, etc.)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>188,550</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1980,7 +2794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2067,412 +2881,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>QUALITÉ DES DONNÉES - VALEURS MANQUANTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Nb manquants</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Taux (%)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>niveau_etudes_cm</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>35077</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Modéré 5–20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>men_id</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>departement</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>commune</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>milieu_residence</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>taille_menage</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>sexe_cm</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>age_cm</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>scolarisation_cm</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>situation_matrimoniale_cm</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>nb_enfants_moins5ans</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>nb_femmes_15_49</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>ratio_dependance</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Complet</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>NOTES MÉTHODOLOGIQUES - DÉCISIONS DE TRAITEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>TRAITEMENT DES VALEURS ABERRANTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Explication</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Âge du CM (age_cm)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Bornes définies : [0, 120] ans. Toute valeur hors de ces bornes est remplacée par NaN. Justification : aucun être humain ne peut avoir un âge négatif ou supérieur à 120 ans.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Taille du ménage (taille_menage)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Seuil fixé au 99e percentile observé = 125 membres. Valeurs &gt; 125 remplacées par NaN. Justification empirique : distribution observée - P50=12, P75=46, P90=78, P99=125.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>CONTRÔLES DE COHÉRENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Explication</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Sexe vs situation matrimoniale</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Un CM de sexe masculin ne peut pas être déclaré épouse en polygamie. Action : situation_matrimoniale_cm - NaN.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>